--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206297</v>
+        <v>121206041</v>
       </c>
       <c r="B3" t="n">
-        <v>90652</v>
+        <v>98071</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612360</v>
+        <v>612445</v>
       </c>
       <c r="R3" t="n">
-        <v>6896878</v>
+        <v>6896868</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206041</v>
+        <v>121206297</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>90652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612445</v>
+        <v>612360</v>
       </c>
       <c r="R4" t="n">
-        <v>6896868</v>
+        <v>6896878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206370</v>
+        <v>121205046</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612401</v>
+        <v>612414</v>
       </c>
       <c r="R2" t="n">
-        <v>6896890</v>
+        <v>6896866</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +800,7 @@
         <v>121206041</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206297</v>
+        <v>121205080</v>
       </c>
       <c r="B4" t="n">
-        <v>90652</v>
+        <v>90717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +921,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612360</v>
+        <v>612414</v>
       </c>
       <c r="R4" t="n">
-        <v>6896878</v>
+        <v>6896866</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,7 +1038,7 @@
         <v>121206569</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1137,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206198</v>
+        <v>121206370</v>
       </c>
       <c r="B6" t="n">
-        <v>74705</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1159,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612374</v>
+        <v>612401</v>
       </c>
       <c r="R6" t="n">
-        <v>6896857</v>
+        <v>6896890</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1241,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121205046</v>
+        <v>121206240</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1289,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612414</v>
+        <v>612360</v>
       </c>
       <c r="R7" t="n">
-        <v>6896866</v>
+        <v>6896878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121205080</v>
+        <v>121206198</v>
       </c>
       <c r="B8" t="n">
-        <v>90707</v>
+        <v>74708</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,43 +1401,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612414</v>
+        <v>612374</v>
       </c>
       <c r="R8" t="n">
-        <v>6896866</v>
+        <v>6896857</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,7 +1500,7 @@
         <v>121206416</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206240</v>
+        <v>121206297</v>
       </c>
       <c r="B10" t="n">
-        <v>90687</v>
+        <v>90662</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,25 +1626,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,7 +1729,7 @@
         <v>121244745</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121205046</v>
+        <v>121206240</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612414</v>
+        <v>612360</v>
       </c>
       <c r="R2" t="n">
-        <v>6896866</v>
+        <v>6896878</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206041</v>
+        <v>121206370</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -830,17 +820,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612445</v>
+        <v>612401</v>
       </c>
       <c r="R3" t="n">
-        <v>6896868</v>
+        <v>6896890</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205080</v>
+        <v>121205066</v>
       </c>
       <c r="B4" t="n">
-        <v>90717</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +929,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206569</v>
+        <v>121206198</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>74708</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,38 +1042,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612298</v>
+        <v>612374</v>
       </c>
       <c r="R5" t="n">
-        <v>6896886</v>
+        <v>6896857</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206370</v>
+        <v>121206297</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>90662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,47 +1154,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612401</v>
+        <v>612360</v>
       </c>
       <c r="R6" t="n">
-        <v>6896890</v>
+        <v>6896878</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,11 +1228,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206240</v>
+        <v>121206416</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,34 +1270,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612360</v>
+        <v>612298</v>
       </c>
       <c r="R7" t="n">
-        <v>6896878</v>
+        <v>6896886</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206198</v>
+        <v>121206569</v>
       </c>
       <c r="B8" t="n">
-        <v>74708</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,38 +1383,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612374</v>
+        <v>612298</v>
       </c>
       <c r="R8" t="n">
-        <v>6896857</v>
+        <v>6896886</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1460,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206416</v>
+        <v>121206041</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,43 +1495,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612298</v>
+        <v>612445</v>
       </c>
       <c r="R9" t="n">
-        <v>6896886</v>
+        <v>6896868</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1577,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206297</v>
+        <v>121205080</v>
       </c>
       <c r="B10" t="n">
-        <v>90662</v>
+        <v>90717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,38 +1607,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612360</v>
+        <v>612414</v>
       </c>
       <c r="R10" t="n">
-        <v>6896878</v>
+        <v>6896866</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206240</v>
+        <v>121205046</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612360</v>
+        <v>612414</v>
       </c>
       <c r="R2" t="n">
-        <v>6896878</v>
+        <v>6896866</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206370</v>
+        <v>121206198</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>74710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612401</v>
+        <v>612374</v>
       </c>
       <c r="R3" t="n">
-        <v>6896890</v>
+        <v>6896857</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205066</v>
+        <v>121206416</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -954,14 +950,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612414</v>
+        <v>612298</v>
       </c>
       <c r="R4" t="n">
-        <v>6896866</v>
+        <v>6896886</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206198</v>
+        <v>121206041</v>
       </c>
       <c r="B5" t="n">
-        <v>74708</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612374</v>
+        <v>612445</v>
       </c>
       <c r="R5" t="n">
-        <v>6896857</v>
+        <v>6896868</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206297</v>
+        <v>121206569</v>
       </c>
       <c r="B6" t="n">
-        <v>90662</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612360</v>
+        <v>612298</v>
       </c>
       <c r="R6" t="n">
-        <v>6896878</v>
+        <v>6896886</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206416</v>
+        <v>121206297</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90674</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,43 +1262,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612298</v>
+        <v>612360</v>
       </c>
       <c r="R7" t="n">
-        <v>6896886</v>
+        <v>6896878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206569</v>
+        <v>121206370</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,17 +1395,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612298</v>
+        <v>612401</v>
       </c>
       <c r="R8" t="n">
-        <v>6896886</v>
+        <v>6896890</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206041</v>
+        <v>121205080</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>90729</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,38 +1500,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612445</v>
+        <v>612414</v>
       </c>
       <c r="R9" t="n">
-        <v>6896868</v>
+        <v>6896866</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1582,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121205080</v>
+        <v>121206240</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
+        <v>90709</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,43 +1630,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612414</v>
+        <v>612360</v>
       </c>
       <c r="R10" t="n">
-        <v>6896866</v>
+        <v>6896878</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,7 +1729,7 @@
         <v>121244745</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206198</v>
+        <v>121206416</v>
       </c>
       <c r="B3" t="n">
-        <v>74710</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612374</v>
+        <v>612298</v>
       </c>
       <c r="R3" t="n">
-        <v>6896857</v>
+        <v>6896886</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206416</v>
+        <v>121206198</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612298</v>
+        <v>612374</v>
       </c>
       <c r="R4" t="n">
-        <v>6896886</v>
+        <v>6896857</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206041</v>
+        <v>121206297</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612445</v>
+        <v>612360</v>
       </c>
       <c r="R5" t="n">
-        <v>6896868</v>
+        <v>6896878</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206569</v>
+        <v>121206370</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,17 +1171,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612298</v>
+        <v>612401</v>
       </c>
       <c r="R6" t="n">
-        <v>6896886</v>
+        <v>6896890</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206297</v>
+        <v>121206569</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,38 +1276,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612360</v>
+        <v>612298</v>
       </c>
       <c r="R7" t="n">
-        <v>6896878</v>
+        <v>6896886</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206370</v>
+        <v>121205080</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>90730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,35 +1388,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612401</v>
+        <v>612414</v>
       </c>
       <c r="R8" t="n">
-        <v>6896890</v>
+        <v>6896866</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121205080</v>
+        <v>121206240</v>
       </c>
       <c r="B9" t="n">
-        <v>90729</v>
+        <v>90710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,43 +1518,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612414</v>
+        <v>612360</v>
       </c>
       <c r="R9" t="n">
-        <v>6896866</v>
+        <v>6896878</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1572,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,12 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206240</v>
+        <v>121206041</v>
       </c>
       <c r="B10" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,25 +1626,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612360</v>
+        <v>612445</v>
       </c>
       <c r="R10" t="n">
-        <v>6896878</v>
+        <v>6896868</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,7 +1729,7 @@
         <v>121244745</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121205046</v>
+        <v>121206569</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612414</v>
+        <v>612298</v>
       </c>
       <c r="R2" t="n">
-        <v>6896866</v>
+        <v>6896886</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206416</v>
+        <v>121206198</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612298</v>
+        <v>612374</v>
       </c>
       <c r="R3" t="n">
-        <v>6896886</v>
+        <v>6896857</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206198</v>
+        <v>121206297</v>
       </c>
       <c r="B4" t="n">
-        <v>74710</v>
+        <v>90678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612374</v>
+        <v>612360</v>
       </c>
       <c r="R4" t="n">
-        <v>6896857</v>
+        <v>6896878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206297</v>
+        <v>121206416</v>
       </c>
       <c r="B5" t="n">
-        <v>90675</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612360</v>
+        <v>612298</v>
       </c>
       <c r="R5" t="n">
-        <v>6896878</v>
+        <v>6896886</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206370</v>
+        <v>121206041</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,26 +1161,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612401</v>
+        <v>612445</v>
       </c>
       <c r="R6" t="n">
-        <v>6896890</v>
+        <v>6896868</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206569</v>
+        <v>121205046</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,38 +1252,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612298</v>
+        <v>612414</v>
       </c>
       <c r="R7" t="n">
-        <v>6896886</v>
+        <v>6896866</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,7 +1365,7 @@
         <v>121205080</v>
       </c>
       <c r="B8" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1505,7 +1491,7 @@
         <v>121206240</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206041</v>
+        <v>121206370</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,17 +1633,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612445</v>
+        <v>612401</v>
       </c>
       <c r="R10" t="n">
-        <v>6896868</v>
+        <v>6896890</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,7 +1729,7 @@
         <v>121244745</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206569</v>
+        <v>121205080</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>90733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612298</v>
+        <v>612414</v>
       </c>
       <c r="R2" t="n">
-        <v>6896886</v>
+        <v>6896866</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206198</v>
+        <v>121206416</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +817,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612374</v>
+        <v>612298</v>
       </c>
       <c r="R3" t="n">
-        <v>6896857</v>
+        <v>6896886</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206297</v>
+        <v>121205046</v>
       </c>
       <c r="B4" t="n">
-        <v>90678</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +930,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612360</v>
+        <v>612414</v>
       </c>
       <c r="R4" t="n">
-        <v>6896878</v>
+        <v>6896866</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206416</v>
+        <v>121206041</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1052,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612298</v>
+        <v>612445</v>
       </c>
       <c r="R5" t="n">
-        <v>6896886</v>
+        <v>6896868</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206041</v>
+        <v>121206297</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1164,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612445</v>
+        <v>612360</v>
       </c>
       <c r="R6" t="n">
-        <v>6896868</v>
+        <v>6896878</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121205046</v>
+        <v>121206240</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612414</v>
+        <v>612360</v>
       </c>
       <c r="R7" t="n">
-        <v>6896866</v>
+        <v>6896878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121205080</v>
+        <v>121206198</v>
       </c>
       <c r="B8" t="n">
-        <v>90733</v>
+        <v>74713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,43 +1392,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612414</v>
+        <v>612374</v>
       </c>
       <c r="R8" t="n">
-        <v>6896866</v>
+        <v>6896857</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,12 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206240</v>
+        <v>121206569</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1500,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612360</v>
+        <v>612298</v>
       </c>
       <c r="R9" t="n">
-        <v>6896878</v>
+        <v>6896886</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206240</v>
+        <v>121206198</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>74713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1280,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612360</v>
+        <v>612374</v>
       </c>
       <c r="R7" t="n">
-        <v>6896878</v>
+        <v>6896857</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206198</v>
+        <v>121206240</v>
       </c>
       <c r="B8" t="n">
-        <v>74713</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,21 +1392,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612374</v>
+        <v>612360</v>
       </c>
       <c r="R8" t="n">
-        <v>6896857</v>
+        <v>6896878</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206198</v>
+        <v>121206240</v>
       </c>
       <c r="B7" t="n">
-        <v>74713</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1280,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612374</v>
+        <v>612360</v>
       </c>
       <c r="R7" t="n">
-        <v>6896857</v>
+        <v>6896878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206240</v>
+        <v>121206198</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>74713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,21 +1392,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612360</v>
+        <v>612374</v>
       </c>
       <c r="R8" t="n">
-        <v>6896878</v>
+        <v>6896857</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121205080</v>
+        <v>121206569</v>
       </c>
       <c r="B2" t="n">
-        <v>90733</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612414</v>
+        <v>612298</v>
       </c>
       <c r="R2" t="n">
-        <v>6896866</v>
+        <v>6896886</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206416</v>
+        <v>121205046</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612298</v>
+        <v>612414</v>
       </c>
       <c r="R3" t="n">
-        <v>6896886</v>
+        <v>6896866</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205046</v>
+        <v>121206416</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,14 +950,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612414</v>
+        <v>612298</v>
       </c>
       <c r="R4" t="n">
-        <v>6896866</v>
+        <v>6896886</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206041</v>
+        <v>121206297</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>90684</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1080,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612445</v>
+        <v>612360</v>
       </c>
       <c r="R5" t="n">
-        <v>6896868</v>
+        <v>6896878</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206297</v>
+        <v>121206370</v>
       </c>
       <c r="B6" t="n">
-        <v>90678</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,38 +1150,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612360</v>
+        <v>612401</v>
       </c>
       <c r="R6" t="n">
-        <v>6896878</v>
+        <v>6896890</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1238,6 +1233,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206240</v>
+        <v>121206198</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>74714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1280,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612360</v>
+        <v>612374</v>
       </c>
       <c r="R7" t="n">
-        <v>6896878</v>
+        <v>6896857</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206198</v>
+        <v>121205080</v>
       </c>
       <c r="B8" t="n">
-        <v>74713</v>
+        <v>90739</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,34 +1392,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612374</v>
+        <v>612414</v>
       </c>
       <c r="R8" t="n">
-        <v>6896857</v>
+        <v>6896866</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206569</v>
+        <v>121206240</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1514,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612298</v>
+        <v>612360</v>
       </c>
       <c r="R9" t="n">
-        <v>6896886</v>
+        <v>6896878</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206370</v>
+        <v>121206041</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,26 +1647,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612401</v>
+        <v>612445</v>
       </c>
       <c r="R10" t="n">
-        <v>6896890</v>
+        <v>6896868</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,7 +1729,7 @@
         <v>121244745</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206569</v>
+        <v>121206416</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sörtjärnen, Sörtjärnen, Mpd</t>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121205046</v>
+        <v>121206370</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612414</v>
+        <v>612401</v>
       </c>
       <c r="R3" t="n">
-        <v>6896866</v>
+        <v>6896890</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206416</v>
+        <v>121205046</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,14 +959,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612298</v>
+        <v>612414</v>
       </c>
       <c r="R4" t="n">
-        <v>6896886</v>
+        <v>6896866</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206297</v>
+        <v>121206198</v>
       </c>
       <c r="B5" t="n">
-        <v>90684</v>
+        <v>74715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1052,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612360</v>
+        <v>612374</v>
       </c>
       <c r="R5" t="n">
-        <v>6896878</v>
+        <v>6896857</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206370</v>
+        <v>121205080</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,35 +1164,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1187,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612401</v>
+        <v>612414</v>
       </c>
       <c r="R6" t="n">
-        <v>6896890</v>
+        <v>6896866</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206198</v>
+        <v>121206240</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1294,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612374</v>
+        <v>612360</v>
       </c>
       <c r="R7" t="n">
-        <v>6896857</v>
+        <v>6896878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121205080</v>
+        <v>121206297</v>
       </c>
       <c r="B8" t="n">
-        <v>90739</v>
+        <v>90685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,47 +1402,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612414</v>
+        <v>612360</v>
       </c>
       <c r="R8" t="n">
-        <v>6896866</v>
+        <v>6896878</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206240</v>
+        <v>121206569</v>
       </c>
       <c r="B9" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,38 +1514,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612360</v>
+        <v>612298</v>
       </c>
       <c r="R9" t="n">
-        <v>6896878</v>
+        <v>6896886</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,7 +1617,7 @@
         <v>121206041</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>121244745</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206416</v>
+        <v>121206297</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>90685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612298</v>
+        <v>612360</v>
       </c>
       <c r="R2" t="n">
-        <v>6896886</v>
+        <v>6896878</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206370</v>
+        <v>121206569</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -825,26 +820,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612401</v>
+        <v>612298</v>
       </c>
       <c r="R3" t="n">
-        <v>6896890</v>
+        <v>6896886</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121205046</v>
+        <v>121206416</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -959,14 +940,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612414</v>
+        <v>612298</v>
       </c>
       <c r="R4" t="n">
-        <v>6896866</v>
+        <v>6896886</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206198</v>
+        <v>121205046</v>
       </c>
       <c r="B5" t="n">
-        <v>74715</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612374</v>
+        <v>612414</v>
       </c>
       <c r="R5" t="n">
-        <v>6896857</v>
+        <v>6896866</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121205080</v>
+        <v>121206198</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>74715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,43 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612414</v>
+        <v>612374</v>
       </c>
       <c r="R6" t="n">
-        <v>6896866</v>
+        <v>6896857</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1390,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206297</v>
+        <v>121205080</v>
       </c>
       <c r="B8" t="n">
-        <v>90685</v>
+        <v>90740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,38 +1374,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612360</v>
+        <v>612414</v>
       </c>
       <c r="R8" t="n">
-        <v>6896878</v>
+        <v>6896866</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1456,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206569</v>
+        <v>121206041</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1538,14 +1524,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612298</v>
+        <v>612445</v>
       </c>
       <c r="R9" t="n">
-        <v>6896886</v>
+        <v>6896868</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1577,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206041</v>
+        <v>121206370</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1647,17 +1633,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612445</v>
+        <v>612401</v>
       </c>
       <c r="R10" t="n">
-        <v>6896868</v>
+        <v>6896890</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121206416</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>121205046</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121206416</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>121205046</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121206416</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>121205046</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121206416</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>121205046</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206297</v>
+        <v>121206240</v>
       </c>
       <c r="B2" t="n">
-        <v>90685</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206569</v>
+        <v>121205080</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612298</v>
+        <v>612414</v>
       </c>
       <c r="R3" t="n">
-        <v>6896886</v>
+        <v>6896866</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Högt upp i en gammal tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,55 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206416</v>
+        <v>121206297</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612298</v>
+        <v>612360</v>
       </c>
       <c r="R4" t="n">
-        <v>6896886</v>
+        <v>6896878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,55 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121205046</v>
+        <v>121206573</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612414</v>
+        <v>612393</v>
       </c>
       <c r="R5" t="n">
-        <v>6896866</v>
+        <v>6896753</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,12 +1120,7 @@
         <v>121206198</v>
       </c>
       <c r="B6" t="n">
-        <v>74715</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,15 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206240</v>
+        <v>121204970</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612360</v>
+        <v>612453</v>
       </c>
       <c r="R7" t="n">
-        <v>6896878</v>
+        <v>6896852</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,15 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121205080</v>
+        <v>121205046</v>
       </c>
       <c r="B8" t="n">
-        <v>90740</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,31 +1342,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1446,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,12 +1416,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Högt upp i en gammal tall</t>
+          <t>Rikligt med spår på en grov tall. Svårt att bedöma ålder på spåren.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,50 +1448,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206041</v>
+        <v>121206416</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hålen, Hålen, Mpd</t>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612445</v>
+        <v>612298</v>
       </c>
       <c r="R9" t="n">
-        <v>6896868</v>
+        <v>6896886</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,15 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206370</v>
+        <v>121206041</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,26 +1588,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612401</v>
+        <v>612445</v>
       </c>
       <c r="R10" t="n">
-        <v>6896890</v>
+        <v>6896868</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera förekomster inom några kvadratmeter</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,15 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121244745</v>
+        <v>121206370</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,24 +1695,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hålen, Ortsjö, Njurunda, Mpd</t>
+          <t>Hålen, Hålen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>612263</v>
+        <v>612401</v>
       </c>
       <c r="R11" t="n">
-        <v>6896815</v>
+        <v>6896890</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,18 +1744,32 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera förekomster inom några kvadratmeter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1830,6 +1785,322 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121206569</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sörtjärnen, Sörtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>612298</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6896886</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121206579</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hålen, Hålen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>612393</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6896753</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121244745</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hålen, Ortsjö, Njurunda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>612263</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6896815</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43818-2024 artfynd.xlsx
+++ b/artfynd/A 43818-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206240</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121205080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206297</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206573</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206198</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121204970</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121205046</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206416</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206041</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206370</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206569</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1999,6 +2059,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206579</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2101,8 +2166,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>